--- a/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:41</t>
+          <t>2026-08-25 10:24:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:43</t>
+          <t>2026-08-25 10:24:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:44</t>
+          <t>2026-08-25 10:24:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:45</t>
+          <t>2026-08-25 10:24:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:45</t>
+          <t>2026-08-25 10:24:29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:45</t>
+          <t>2026-08-25 10:24:29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:45</t>
+          <t>2026-08-25 10:24:29</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:45</t>
+          <t>2026-08-25 10:24:29</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:45</t>
+          <t>2026-08-25 10:24:29</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.45%2375</t>
+          <t>+1.05%2400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2375</v>
+        <v>2400</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12.72%4,500,000</t>
+          <t>12.71%4,500,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12.72%</t>
+          <t>12.71%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-4.4%5430</t>
+          <t>+3.04%5595</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>+3.04%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5430</v>
+        <v>5595</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.05%1,400,000</t>
+          <t>9.22%1,400,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.05%</t>
+          <t>9.22%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+7.66%14410</t>
+          <t>-0.87%14285</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14410</v>
+        <v>14285</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.75%510,000</t>
+          <t>8.57%510,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.75%</t>
+          <t>8.57%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-5.11%501</t>
+          <t>+1.8%510</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.11%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.35%14,000,000</t>
+          <t>8.40%14,000,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.35%</t>
+          <t>8.40%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.92%1075</t>
+          <t>+1.86%1095</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1075</v>
+        <v>1095</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.40%5,000,000</t>
+          <t>6.44%5,000,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.40%</t>
+          <t>6.44%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.54%551</t>
+          <t>-1.27%544</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.05%7,700,000</t>
+          <t>4.93%7,700,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.05%</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.72%6300</t>
+          <t>+2.22%6440</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6300</v>
+        <v>6440</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.50%600,000</t>
+          <t>4.55%600,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2454聯發科技</t>
+          <t>8046南亞電路</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.66%3765</t>
+          <t>+2.2%1160</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3765</v>
+        <v>1160</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.48%1,000,000</t>
+          <t>4.44%3,250,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>4.44%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1000000</v>
+        <v>3250000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,25 +992,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8046南亞電路</t>
+          <t>2454聯發科技</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>-0.8%3735</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1135</v>
+        <v>3735</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.39%3,250,000</t>
+          <t>4.39%1,000,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3250000</v>
+        <v>1000000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.83%5565</t>
+          <t>+0.63%5600</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5565</v>
+        <v>5600</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.37%660,000</t>
+          <t>4.35%660,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.37%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.72%2070</t>
+          <t>+3.33%2950</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2070</v>
+        <v>2950</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.31%1,750,000</t>
+          <t>4.34%1,250,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1750000</v>
+        <v>1250000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3017奇鋐科技</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.35%2855</t>
+          <t>+2.06%1485</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2855</v>
+        <v>1485</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.25%1,250,000</t>
+          <t>4.19%2,400,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>4.19%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1250000</v>
+        <v>2400000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.68%1455</t>
+          <t>-1.93%2030</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1455</v>
+        <v>2030</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.16%2,400,000</t>
+          <t>4.18%1,750,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>2400000</v>
+        <v>1750000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.1%794</t>
+          <t>+5.16%835</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+5.16%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>794</v>
+        <v>835</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.88%4,100,000</t>
+          <t>4.03%4,100,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:26</t>
+          <t>2026-08-25 17:36:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.34%6255</t>
+          <t>-0.72%6210</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6255</v>
+        <v>6210</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.83%380,000</t>
+          <t>2.78%380,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,27 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.31%2765</t>
+          <t>+7.05%2960</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.31%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2765</t>
-        </is>
+          <t>+7.05%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2960</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.30%700,000</t>
+          <t>2.44%700,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1452,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1482,40 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+2.89%2135</t>
+          <t>+1.89%15400</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+2.89%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
+          <t>+1.89%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>15400</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.24%880,000</t>
+          <t>2.18%120,500</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>880000</v>
+        <v>120500</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1545,40 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.53%15115</t>
+          <t>-2.34%2085</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.53%</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>15115</t>
-        </is>
+          <t>-2.34%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2085</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.17%120,500</t>
+          <t>2.16%880,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>120500</v>
+        <v>880000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,27 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-4.45%5155</t>
+          <t>+0.97%5205</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-4.45%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>5155</t>
-        </is>
+          <t>+0.97%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>5205</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.09%340,000</t>
+          <t>2.08%340,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1641,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,27 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.63%643</t>
+          <t>-2.33%628</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.63%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
+          <t>-2.33%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>628</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.07%2,700,000</t>
+          <t>2.00%2,700,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1704,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,27 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-4.01%5385</t>
+          <t>+6.22%5720</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.01%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>5385</t>
-        </is>
+          <t>+6.22%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>5720</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1767,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,27 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.85%592</t>
+          <t>-0.17%591</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.85%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>591</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.01%9,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1830,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,32 +1846,30 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5347世界先進</t>
+          <t>2382廣達電腦</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.33%151</t>
+          <t>+1.08%328.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.33%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
+          <t>+1.08%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>328.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1910,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1923,40 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3044健鼎科技</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.96%450</t>
+          <t>-1.8%246</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.96%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
+          <t>-1.8%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>246</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,40 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2317鴻海精密</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-9.89%2050</t>
+          <t>-0.21%243</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.89%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>243</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2049,36 +2029,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3231緯創資通</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0%175.5</t>
+          <t>+1.22%2075</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>175.5</t>
-        </is>
+          <t>+1.22%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2075</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2099,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2112,32 +2090,30 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.67%200.5</t>
+          <t>-5.07%1965</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.67%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>200.5</t>
-        </is>
+          <t>-5.07%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1965</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2145,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2175,32 +2151,30 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2412中華電信</t>
+          <t>2308台達電子</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0%136.5</t>
+          <t>-1.44%1710</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
+          <t>-1.44%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1710</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2208,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:27</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2238,36 +2212,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>3231緯創資通</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.02%239</t>
+          <t>+1.71%178.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.02%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
+          <t>+1.71%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>178.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0%1,450</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1450</v>
+        <v>9000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2288,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2297,42 +2269,42 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1216統一企業</t>
+          <t>5347世界先進</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.13%77.4</t>
+          <t>-0.33%150.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>77.40000000000001</v>
+        <v>150.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2349,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2362,34 +2334,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2404漢唐集成</t>
+          <t>2881富邦金融</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.47%1065</t>
+          <t>+7.2%141.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+7.2%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1065</v>
+        <v>141.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2410,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2423,30 +2395,30 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2357華碩電腦</t>
+          <t>2404漢唐集成</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.22%923</t>
+          <t>+0.47%1070</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>923</v>
+        <v>1070</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2471,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2484,30 +2456,30 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>2357華碩電腦</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.43%2070</t>
+          <t>+0.22%925</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2070</v>
+        <v>925</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2532,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2545,34 +2517,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2379瑞昱半導</t>
+          <t>2882國泰金融</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.28%716</t>
+          <t>+4.15%103</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+4.15%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>716</v>
+        <v>103</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2593,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2606,34 +2578,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2382廣達電腦</t>
+          <t>2379瑞昱半導</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.09%325</t>
+          <t>+1.96%730</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.96%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>325</v>
+        <v>730</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2654,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2667,34 +2639,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2308台達電子</t>
+          <t>2885元大金融</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.86%1735</t>
+          <t>0%62.4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1735</v>
+        <v>62.4</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,360</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1000</v>
+        <v>9360</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2715,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2728,34 +2700,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2313華通電腦</t>
+          <t>2891中國信託</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.47%212.5</t>
+          <t>+1.42%64.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>212.5</v>
+        <v>64.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0%1,253</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1253</v>
+        <v>9000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2776,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2789,34 +2761,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2317鴻海精密</t>
+          <t>3044健鼎科技</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.81%243.5</t>
+          <t>+2.89%463</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>243.5</v>
+        <v>463</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2837,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2850,21 +2822,21 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>2890永豐金融</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.4%250.5</t>
+          <t>+0.9%39.3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>250.5</v>
+        <v>39.3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2911,25 +2883,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2880華南金融</t>
+          <t>2886兆豐金融</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.88%39.25</t>
+          <t>+0.32%47</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>39.25</v>
+        <v>47</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0%9,090</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2938,7 +2910,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>9090</v>
+        <v>9000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2959,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2972,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2881富邦金融</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.49%132</t>
+          <t>+0.21%239.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>132</v>
+        <v>239.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,450</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2999,7 +2971,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>9000</v>
+        <v>1450</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -3020,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3033,21 +3005,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2882國泰金融</t>
+          <t>2884玉山金融</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.59%98.9</t>
+          <t>+2.23%39</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.59%</t>
+          <t>+2.23%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>98.90000000000001</v>
+        <v>39</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3094,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2883凱基金融</t>
+          <t>2880華南金融</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.74%31</t>
+          <t>+1.4%39.8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>31</v>
+        <v>39.8</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%9,090</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3121,7 +3093,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9000</v>
+        <v>9090</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3142,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:28</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3155,21 +3127,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2884玉山金融</t>
+          <t>2883凱基金融</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.39%38.15</t>
+          <t>+2.26%31.7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>38.15</v>
+        <v>31.7</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:29</t>
+          <t>2026-08-25 17:36:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3212,31 +3184,29 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2885元大金融</t>
+          <t>2887台新新光</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.5%62.4</t>
+          <t>+1.78%37.15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.5%</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
+          <t>+1.78%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>37.15</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0%9,360</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3245,7 +3215,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9360</v>
+        <v>9000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3266,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:29</t>
+          <t>2026-08-25 17:36:13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3279,27 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2886兆豐金融</t>
+          <t>2313華通電腦</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.21%46.85</t>
+          <t>+2.35%217.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>46.85</t>
-        </is>
+          <t>+2.35%</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>217.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,253</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3308,7 +3276,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>9000</v>
+        <v>1253</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3329,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:29</t>
+          <t>2026-08-25 17:36:13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3342,27 +3310,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2887台新新光</t>
+          <t>2912統一超商</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.01%36.5</t>
+          <t>+0.22%224</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.01%</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>36.5</t>
-        </is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>224</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3371,7 +3337,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -3392,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:29</t>
+          <t>2026-08-25 17:36:13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3405,27 +3371,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2890永豐金融</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.64%38.95</t>
+          <t>-1%198.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.64%</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>38.95</t>
-        </is>
+          <t>-1%</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>198.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3434,7 +3398,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3455,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:29</t>
+          <t>2026-08-25 17:36:13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3468,27 +3432,25 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2891中國信託</t>
+          <t>2412中華電信</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.15%63.6</t>
+          <t>0%136.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.15%</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>63.6</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>136.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3497,7 +3459,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3518,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:29</t>
+          <t>2026-08-25 17:36:13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3531,23 +3493,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2912統一超商</t>
+          <t>1216統一企業</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0%223.5</t>
+          <t>+0.65%77.9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>223.5</t>
-        </is>
+          <t>+0.65%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>77.90000000000001</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:09</t>
+          <t>2026-08-25 19:51:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:10</t>
+          <t>2026-08-25 19:51:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:11</t>
+          <t>2026-08-25 19:51:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:13</t>
+          <t>2026-08-25 19:51:04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:13</t>
+          <t>2026-08-25 19:51:04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:13</t>
+          <t>2026-08-25 19:51:04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:13</t>
+          <t>2026-08-25 19:51:04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:13</t>
+          <t>2026-08-25 19:51:04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:00</t>
+          <t>2026-08-25 21:09:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:01</t>
+          <t>2026-08-25 21:09:21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:02</t>
+          <t>2026-08-25 21:09:22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:04</t>
+          <t>2026-08-25 21:09:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:04</t>
+          <t>2026-08-25 21:09:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:04</t>
+          <t>2026-08-25 21:09:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:04</t>
+          <t>2026-08-25 21:09:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:04</t>
+          <t>2026-08-25 21:09:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:19</t>
+          <t>2026-08-25 21:27:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:21</t>
+          <t>2026-08-25 21:27:57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:22</t>
+          <t>2026-08-25 21:27:58</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:23</t>
+          <t>2026-08-25 21:27:59</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:23</t>
+          <t>2026-08-25 21:27:59</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:23</t>
+          <t>2026-08-25 21:27:59</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:23</t>
+          <t>2026-08-25 21:27:59</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:23</t>
+          <t>2026-08-25 21:27:59</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:55</t>
+          <t>2026-08-25 21:31:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:57</t>
+          <t>2026-08-25 21:31:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:58</t>
+          <t>2026-08-25 21:31:20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:59</t>
+          <t>2026-08-25 21:31:22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:59</t>
+          <t>2026-08-25 21:31:22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:59</t>
+          <t>2026-08-25 21:31:22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:59</t>
+          <t>2026-08-25 21:31:22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:59</t>
+          <t>2026-08-25 21:31:22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:18</t>
+          <t>2026-08-25 22:04:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:19</t>
+          <t>2026-08-25 22:04:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:20</t>
+          <t>2026-08-25 22:04:06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:22</t>
+          <t>2026-08-25 22:04:07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:22</t>
+          <t>2026-08-25 22:04:07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:22</t>
+          <t>2026-08-25 22:04:07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:22</t>
+          <t>2026-08-25 22:04:07</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:22</t>
+          <t>2026-08-25 22:04:07</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
